--- a/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -338,7 +338,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-strahlentherapie-stellungzurop</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-strahlentherapie-stellungzurop</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
@@ -857,7 +857,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="88.703125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="93.1015625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
+++ b/branches/dev/StructureDefinition-mii-ex-onko-strahlentherapie-stellungzurop.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
